--- a/artfynd/S 1319-2026 artfynd.xlsx
+++ b/artfynd/S 1319-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -797,6 +802,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114140839</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610372</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112610373</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114029678</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1229,6 +1254,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114028697</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114029144</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114029407</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,6 +1613,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112552203</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79749880</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,6 +1837,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130188226</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1899,8 +1954,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130188225</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1319-2026 artfynd.xlsx
+++ b/artfynd/S 1319-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,48 +1728,52 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130188226</v>
+        <v>136480988</v>
       </c>
       <c r="B11" t="n">
-        <v>57141</v>
+        <v>80588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Boden-Skellefteå, Nb</t>
+          <t>Åkerholmen, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>785005</v>
+        <v>771184</v>
       </c>
       <c r="R11" t="n">
-        <v>7316676</v>
+        <v>7322989</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1793,27 +1797,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>NVI (C250260) Calluna AB</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1828,49 +1832,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jonas Mattsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Julia Svensson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130188226</t>
+          <t>https://artportalen.se/Sighting/136480988</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130188225</v>
+        <v>130188226</v>
       </c>
       <c r="B12" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>782041</v>
+        <v>785005</v>
       </c>
       <c r="R12" t="n">
-        <v>7315611</v>
+        <v>7316676</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1915,7 +1919,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1925,7 +1929,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1950,11 +1954,128 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olle Kvarnbäck</t>
+          <t>Julia Svensson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130188226</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130188225</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Boden-Skellefteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>782041</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7315611</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Kvarnbäck</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130188225</t>
         </is>
@@ -1973,6 +2094,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1319-2026 artfynd.xlsx
+++ b/artfynd/S 1319-2026 artfynd.xlsx
@@ -1731,7 +1731,7 @@
         <v>136480988</v>
       </c>
       <c r="B11" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
